--- a/natiga.xlsx
+++ b/natiga.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\natiga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\excel2web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45DEE93-8D36-4B68-A433-7CDFD5A3053B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523E959D-9E07-4413-A17F-FD8584D545EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -186,13 +189,13 @@
     <t>تاجر 4</t>
   </si>
   <si>
-    <t>تاجر 5</t>
-  </si>
-  <si>
     <t>الكترونيات</t>
   </si>
   <si>
     <t>مواد غذائة</t>
+  </si>
+  <si>
+    <t>تاجر 515</t>
   </si>
 </sst>
 </file>
@@ -206,13 +209,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -521,15 +524,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="11" max="11" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +582,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
@@ -626,7 +629,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
@@ -672,7 +675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>103</v>
       </c>
@@ -718,7 +721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>104</v>
       </c>
@@ -764,7 +767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>105</v>
       </c>
@@ -815,12 +818,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4C2F65-848E-4F2D-8900-3FED217B68F5}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -843,7 +846,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
@@ -869,7 +872,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
@@ -895,7 +898,7 @@
         <v>9800</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>103</v>
       </c>
@@ -921,7 +924,7 @@
         <v>8400</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>104</v>
       </c>
@@ -947,7 +950,7 @@
         <v>7700</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>105</v>
       </c>
@@ -981,12 +984,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2EA4E8D-5707-4972-AB13-FE48116354D9}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>35</v>
       </c>
@@ -1003,12 +1006,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>40</v>
@@ -1020,12 +1023,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
         <v>41</v>
@@ -1037,12 +1040,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
@@ -1054,12 +1057,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
@@ -1071,12 +1074,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
         <v>44</v>
@@ -1085,7 +1088,7 @@
         <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1097,12 +1100,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E3CB42F-AF0E-4E3F-A20C-5A8A88261D1B}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
@@ -1151,7 +1154,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
@@ -1174,7 +1177,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>103</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>104</v>
       </c>
@@ -1220,7 +1223,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>105</v>
       </c>
@@ -1251,9 +1254,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7044726-76AE-4666-B236-7A5C0357BDA7}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1279,7 +1282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
@@ -1302,7 +1305,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
@@ -1325,7 +1328,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>103</v>
       </c>
@@ -1348,7 +1351,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>104</v>
       </c>
@@ -1371,7 +1374,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>105</v>
       </c>
